--- a/Suarez_Gallup_1981/Suarez_Gallup_1981_registry_rows.xlsx
+++ b/Suarez_Gallup_1981/Suarez_Gallup_1981_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R00999d62f816466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R5c4265b76abf4325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R58b97e912bf14e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Re38c5ab5ea1b4382"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rbc0a9161670c4ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R0dc33369850b4fd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Mirror/mark-test outcomes across chimpanzees, orangutans and gorillas</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Results / figures / tables: item selection pending</x:v>
+        <x:v>Figure 3: Gorilla mark-directed responses by condition and marked location</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap
@@ -350,13 +350,115 @@
         <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 4 / printed p. 178. Preserve wrist versus brow/ear responses and pre-test versus mirror-test conditions; retain sample/protocol from Methods.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="180" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Suarez_Gallup_1981</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="str">
+        <x:v>Mirror/mark-test outcomes across chimpanzees, orangutans and gorillas</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>Figure 7: Orangutan mark-directed responses by condition and marked location</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap
+Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued.
+Original source note: Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>Verified in EndNote full text — PDF p. 6 / printed p. 180. Single orangutan; preserve wrist versus brow and pre-test versus test conditions.</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="180" customHeight="1">
+      <x:c r="A4" s="3" t="str">
+        <x:v>Suarez_Gallup_1981</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="str">
+        <x:v>Mirror/mark-test outcomes across chimpanzees, orangutans and gorillas</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="str">
+        <x:v>Figure 11: Chimpanzee mark-directed responses after the longer exposure protocol</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap
+Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued.
+Original source note: Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="str">
+        <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="str">
+        <x:v>Verified in EndNote full text — PDF p. 8 / printed p. 182. Totals combined across two chimpanzees; preserve aggregate status and exposure protocol.</x:v>
+      </x:c>
+      <x:c r="I4" s="3" t="str">
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="str">
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="180" customHeight="1">
+      <x:c r="A5" s="3" t="str">
+        <x:v>Suarez_Gallup_1981</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="str">
+        <x:v>Mirror/mark-test outcomes across chimpanzees, orangutans and gorillas</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="str">
+        <x:v>Table 2: Individual chimpanzee mark responses after four days of exposure</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap
+Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued.
+Original source note: Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="str">
+        <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="str">
+        <x:v>Verified in EndNote full text — PDF p. 9 / printed p. 183. Hoboh and William, wrist/brow and pre-test/test conditions. Methods report accidental loss of most brow dye for William; do not interpret his result as an unqualified failure. Keep this shorter protocol distinct from Figure 11.</x:v>
+      </x:c>
+      <x:c r="I5" s="3" t="str">
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="str">
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +610,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Suarez, S. D., &amp; Gallup, G. G., Jr. (1981). Self-recognition in chimpanzees and orangutans, but not gorillas. Journal of Human Evolution, 10(2), 175–188. https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Figure 3</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +629,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Suarez_Gallup_1981. Target: Results / figures / tables: item selection pending. Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 4 / printed p. 178. Preserve wrist versus brow/ear responses and pre-test versus mirror-test conditions; retain sample/protocol from Methods. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
@@ -550,7 +654,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Mirror/mark-test outcomes across chimpanzees, orangutans and gorillas</x:v>
+        <x:v>Gorilla mark-directed responses by condition and marked location</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -570,6 +674,207 @@
         <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
       </x:c>
       <x:c r="AH2" s="3" t="str">
+        <x:v>Pending — no snapshot created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="200" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>Suarez, S. D., &amp; Gallup, G. G., Jr. (1981). Self-recognition in chimpanzees and orangutans, but not gorillas. Journal of Human Evolution, 10(2), 175–188. https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3" t="str">
+        <x:v>Figure 7</x:v>
+      </x:c>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="6"/>
+      <x:c r="K3" s="6"/>
+      <x:c r="L3" s="6"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="3" t="str">
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Suarez_Gallup_1981. Target: Results / figures / tables: item selection pending. Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 6 / printed p. 180. Single orangutan; preserve wrist versus brow and pre-test versus test conditions. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+      <x:c r="P3" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
+      </x:c>
+      <x:c r="Q3" s="3"/>
+      <x:c r="R3" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="S3" s="3"/>
+      <x:c r="T3" s="3" t="str">
+        <x:v>Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="U3" s="3"/>
+      <x:c r="V3" s="3" t="str">
+        <x:v>Mirror recognition</x:v>
+      </x:c>
+      <x:c r="W3" s="3" t="str">
+        <x:v>Primates</x:v>
+      </x:c>
+      <x:c r="X3" s="3" t="str">
+        <x:v>Orangutan mark-directed responses by condition and marked location</x:v>
+      </x:c>
+      <x:c r="Y3" s="3"/>
+      <x:c r="Z3" s="3"/>
+      <x:c r="AA3" s="3" t="str">
+        <x:v>Comparative mirror and mark tests</x:v>
+      </x:c>
+      <x:c r="AB3" s="3" t="str">
+        <x:v>Behavioural observation (retain endpoint, individual and condition)</x:v>
+      </x:c>
+      <x:c r="AC3" s="3"/>
+      <x:c r="AD3" s="3"/>
+      <x:c r="AE3" s="3" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+      <x:c r="AF3" s="3"/>
+      <x:c r="AG3" s="3" t="str">
+        <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
+      </x:c>
+      <x:c r="AH3" s="3" t="str">
+        <x:v>Pending — no snapshot created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="200" customHeight="1">
+      <x:c r="A4" s="3" t="str">
+        <x:v>Suarez, S. D., &amp; Gallup, G. G., Jr. (1981). Self-recognition in chimpanzees and orangutans, but not gorillas. Journal of Human Evolution, 10(2), 175–188. https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="3"/>
+      <x:c r="D4" s="3" t="str">
+        <x:v>Figure 11</x:v>
+      </x:c>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
+      <x:c r="L4" s="6"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="3" t="str">
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
+      </x:c>
+      <x:c r="O4" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Suarez_Gallup_1981. Target: Results / figures / tables: item selection pending. Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 8 / printed p. 182. Totals combined across two chimpanzees; preserve aggregate status and exposure protocol. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+      <x:c r="P4" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
+      </x:c>
+      <x:c r="Q4" s="3"/>
+      <x:c r="R4" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="S4" s="3"/>
+      <x:c r="T4" s="3" t="str">
+        <x:v>Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="U4" s="3"/>
+      <x:c r="V4" s="3" t="str">
+        <x:v>Mirror recognition</x:v>
+      </x:c>
+      <x:c r="W4" s="3" t="str">
+        <x:v>Primates</x:v>
+      </x:c>
+      <x:c r="X4" s="3" t="str">
+        <x:v>Chimpanzee mark-directed responses after the longer exposure protocol</x:v>
+      </x:c>
+      <x:c r="Y4" s="3"/>
+      <x:c r="Z4" s="3"/>
+      <x:c r="AA4" s="3" t="str">
+        <x:v>Comparative mirror and mark tests</x:v>
+      </x:c>
+      <x:c r="AB4" s="3" t="str">
+        <x:v>Behavioural observation (retain endpoint, individual and condition)</x:v>
+      </x:c>
+      <x:c r="AC4" s="3"/>
+      <x:c r="AD4" s="3"/>
+      <x:c r="AE4" s="3" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+      <x:c r="AF4" s="3"/>
+      <x:c r="AG4" s="3" t="str">
+        <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
+      </x:c>
+      <x:c r="AH4" s="3" t="str">
+        <x:v>Pending — no snapshot created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="200" customHeight="1">
+      <x:c r="A5" s="3" t="str">
+        <x:v>Suarez, S. D., &amp; Gallup, G. G., Jr. (1981). Self-recognition in chimpanzees and orangutans, but not gorillas. Journal of Human Evolution, 10(2), 175–188. https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="B5" s="6"/>
+      <x:c r="C5" s="3"/>
+      <x:c r="D5" s="3" t="str">
+        <x:v>Table 2</x:v>
+      </x:c>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="6"/>
+      <x:c r="H5" s="6"/>
+      <x:c r="I5" s="6"/>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6"/>
+      <x:c r="L5" s="6"/>
+      <x:c r="M5" s="6"/>
+      <x:c r="N5" s="3" t="str">
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
+      </x:c>
+      <x:c r="O5" s="3" t="str">
+        <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Suarez_Gallup_1981. Target: Results / figures / tables: item selection pending. Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 9 / printed p. 183. Hoboh and William, wrist/brow and pre-test/test conditions. Methods report accidental loss of most brow dye for William; do not interpret his result as an unqualified failure. Keep this shorter protocol distinct from Figure 11. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/3516616688/Suarez-1981-Self-recognition in chimpanzees an.pdf</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="str">
+        <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
+      </x:c>
+      <x:c r="Q5" s="3"/>
+      <x:c r="R5" s="3" t="str">
+        <x:v>https://doi.org/10.1016/S0047-2484(81)80016-4</x:v>
+      </x:c>
+      <x:c r="S5" s="3"/>
+      <x:c r="T5" s="3" t="str">
+        <x:v>Preserve individual results and baseline/control conditions. Negative gorilla results concern this sample and protocol; compare with Posada_Colell_2007 rather than assigning a permanent species failure.</x:v>
+      </x:c>
+      <x:c r="U5" s="3"/>
+      <x:c r="V5" s="3" t="str">
+        <x:v>Mirror recognition</x:v>
+      </x:c>
+      <x:c r="W5" s="3" t="str">
+        <x:v>Primates</x:v>
+      </x:c>
+      <x:c r="X5" s="3" t="str">
+        <x:v>Individual chimpanzee mark responses after four days of exposure</x:v>
+      </x:c>
+      <x:c r="Y5" s="3"/>
+      <x:c r="Z5" s="3"/>
+      <x:c r="AA5" s="3" t="str">
+        <x:v>Comparative mirror and mark tests</x:v>
+      </x:c>
+      <x:c r="AB5" s="3" t="str">
+        <x:v>Behavioural observation (retain endpoint, individual and condition)</x:v>
+      </x:c>
+      <x:c r="AC5" s="3"/>
+      <x:c r="AD5" s="3"/>
+      <x:c r="AE5" s="3" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+      <x:c r="AF5" s="3"/>
+      <x:c r="AG5" s="3" t="str">
+        <x:v>Review/compilation coverage has not been checked at observation level. Keep as a reference pointer. Extract only a required species, individual, condition or endpoint absent from the chosen compilation, or to resolve a specific ambiguity. No primary extraction is queued. Use existing dataset values first, then a suitable compilation with original-source links. Extract a primary paper only for a documented missing observation/condition or ambiguity. A new folder or DOI is not evidence of new data. Shared observations count once; unresolved overlap stays on hold.</x:v>
+      </x:c>
+      <x:c r="AH5" s="3" t="str">
         <x:v>Pending — no snapshot created</x:v>
       </x:c>
     </x:row>
@@ -703,7 +1008,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="100" customHeight="1">
@@ -711,7 +1016,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -995,13 +1300,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAE94E6-D7C8-4954-85D1-7808DDF45234}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DAEB0C1-C60A-474C-89FD-379B50552551}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B132B596-E4B5-49E5-86ED-B238A100A1D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3A4557A-F814-4EE1-92CE-20D60680E691}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50BD8EF7-F2AE-481C-A2C3-440F8D5F04FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD8BC2A-98F9-45AB-92BE-58197B9652E2}"/>
 </file>